--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487509_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487509_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.300800000000001</v>
+        <v>9.1671</v>
       </c>
       <c r="E2" t="n">
         <v>6.6732</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6276</v>
+        <v>2.4939</v>
       </c>
       <c r="G2" t="n">
         <v>6.8376</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4632</v>
+        <v>0.3295</v>
       </c>
       <c r="T2" t="n">
         <v>-0.09</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5531</v>
+        <v>0.4195</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6017</v>
+        <v>6.3306</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2754</v>
+        <v>5.7638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3263</v>
+        <v>0.5668</v>
       </c>
       <c r="G3" t="n">
         <v>5.8949</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5697</v>
+        <v>0.2986</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4734</v>
+        <v>-0.0382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0963</v>
+        <v>0.3369</v>
       </c>
       <c r="V3" t="n">
         <v>0.3329</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6476</v>
+        <v>4.9638</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7434</v>
+        <v>3.8458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9042</v>
+        <v>1.118</v>
       </c>
       <c r="G4" t="n">
         <v>3.8268</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0421</v>
+        <v>0.2741</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0882</v>
+        <v>0.1906</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1303</v>
+        <v>0.0835</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.864</v>
+        <v>2.5895</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9081</v>
+        <v>2.4198</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0441</v>
+        <v>0.1698</v>
       </c>
       <c r="G5" t="n">
         <v>2.1512</v>
@@ -844,13 +844,13 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6408</v>
+        <v>0.0847</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5346</v>
+        <v>-0.0229</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1062</v>
+        <v>0.1076</v>
       </c>
       <c r="V5" t="n">
         <v>0.9412</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3938</v>
+        <v>1.0566</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7735</v>
+        <v>2.5659</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3798</v>
+        <v>-1.5093</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4427</v>
+        <v>2.5074</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5543</v>
+        <v>-0.0592</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1116</v>
+        <v>2.5665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7583</v>
+        <v>3.7146</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3946</v>
+        <v>1.1637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3637</v>
+        <v>2.551</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.201</v>
+        <v>-1.2073</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9489</v>
+        <v>-1.2228</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2521</v>
+        <v>0.0156</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>2.878</v>
+        <v>0.2151</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7191</v>
+        <v>0.4964</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1589</v>
+        <v>-0.2813</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8249</v>
+        <v>-1.2742</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1003</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3277</v>
+        <v>0.1356</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0776</v>
+        <v>0.1911</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7499</v>
+        <v>-0.0555</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5074</v>
+        <v>-0.0181</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0592</v>
+        <v>-0.331</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5665</v>
+        <v>0.3129</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7146</v>
+        <v>1.2527</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1637</v>
+        <v>0.5512</v>
       </c>
       <c r="L7" t="n">
-        <v>2.551</v>
+        <v>0.7015</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2073</v>
+        <v>-1.2708</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2228</v>
+        <v>-0.8822</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0156</v>
+        <v>-0.3886</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4862</v>
+        <v>0.2332</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0081</v>
+        <v>-0.0823</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5219</v>
+        <v>0.3155</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2742</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0018</v>
+        <v>-0.155</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3205</v>
+        <v>0.5455</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3187</v>
+        <v>-0.7005</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0181</v>
+        <v>-0.4427</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.331</v>
+        <v>-0.5543</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3129</v>
+        <v>0.1116</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2527</v>
+        <v>0.7583</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5512</v>
+        <v>0.3946</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7015</v>
+        <v>0.3637</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2708</v>
+        <v>-1.201</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8822</v>
+        <v>-0.9489</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3886</v>
+        <v>-0.2521</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0958</v>
+        <v>1.3292</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.594</v>
+        <v>0.4911</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6898</v>
+        <v>0.8381</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.083</v>
+        <v>-1.2747</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7412</v>
+        <v>-2.6388</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6582</v>
+        <v>1.3641</v>
       </c>
       <c r="G9" t="n">
         <v>0.2962</v>
@@ -1156,13 +1156,13 @@
         <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7544</v>
+        <v>0.5627</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>-0.0471</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9038</v>
+        <v>0.6098</v>
       </c>
       <c r="V9" t="n">
         <v>0.6083</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7939</v>
+        <v>-1.9005</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1776</v>
+        <v>-3.3123</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6163</v>
+        <v>1.4118</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8095</v>
+        <v>-3.9687</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2385</v>
+        <v>-1.7103</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.571</v>
+        <v>-2.2584</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-1.9604</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7791</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3241</v>
+        <v>-1.8802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2646</v>
+        <v>-2.0083</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0176</v>
+        <v>-1.6301</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2469</v>
+        <v>-0.3782</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>2.9377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3553</v>
+        <v>-0.1276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6534</v>
+        <v>-0.277</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2981</v>
+        <v>0.1494</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8353</v>
+        <v>-2.4915</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9263</v>
+        <v>-1.7683</v>
       </c>
       <c r="F11" t="n">
-        <v>1.091</v>
+        <v>-0.7232</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9687</v>
+        <v>-1.8095</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7103</v>
+        <v>-0.2385</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2584</v>
+        <v>-1.571</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9604</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.7791</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8802</v>
+        <v>-1.3241</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0083</v>
+        <v>-1.2646</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6301</v>
+        <v>-1.0176</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3782</v>
+        <v>-0.2469</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9377</v>
+        <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0624</v>
+        <v>-0.0529</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.891</v>
+        <v>-0.2441</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1714</v>
+        <v>0.1911</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2166</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3329</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.4216</v>
+        <v>18.4215</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2856</v>
+        <v>14.2857</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1359</v>
+        <v>4.135899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>15.2751</v>
@@ -1381,7 +1381,7 @@
         <v>-1.1568</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999932285e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.6469</v>
@@ -1390,13 +1390,13 @@
         <v>16.647</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1467</v>
+        <v>3.146599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3764000000000001</v>
+        <v>0.3764999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7702</v>
+        <v>2.7701</v>
       </c>
       <c r="V12" t="n">
         <v>-0.000100000000000211</v>
@@ -1405,7 +1405,7 @@
         <v>4.9691</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.969199999999999</v>
+        <v>-4.9692</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6961</v>
+        <v>2.9217</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8039</v>
+        <v>2.1899</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8923</v>
+        <v>0.7319</v>
       </c>
       <c r="G13" t="n">
         <v>1.4695</v>
@@ -1468,13 +1468,13 @@
         <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1483</v>
+        <v>-0.6261</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0018</v>
+        <v>-0.6158</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1501</v>
+        <v>-0.0103</v>
       </c>
       <c r="V13" t="n">
         <v>1.8825</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2825</v>
+        <v>1.4906</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7863</v>
+        <v>3.9676</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5037</v>
+        <v>-2.477</v>
       </c>
       <c r="G14" t="n">
         <v>0.8048999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1447</v>
+        <v>0.3527</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2151</v>
+        <v>0.3964</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0704</v>
+        <v>-0.0437</v>
       </c>
       <c r="V14" t="n">
         <v>0.3329</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9508</v>
+        <v>-0.9833</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.7173</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1852</v>
+        <v>-1.7006</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4956</v>
+        <v>-2.4718</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0194</v>
+        <v>-2.6379</v>
       </c>
       <c r="I15" t="n">
-        <v>0.515</v>
+        <v>0.1661</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2873</v>
+        <v>1.6343</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0003</v>
+        <v>0.5545</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.713</v>
+        <v>1.0797</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2083</v>
+        <v>-4.1061</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0197</v>
+        <v>-3.1925</v>
       </c>
       <c r="O15" t="n">
-        <v>1.228</v>
+        <v>-0.9136</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>3.1336</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5155999999999999</v>
+        <v>-0.8456</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.7258</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0767</v>
+        <v>-0.1198</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1578</v>
+        <v>1.159</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6659</v>
+        <v>1.7673</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5614</v>
+        <v>-1.5114</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1014</v>
+        <v>-1.3796</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.46</v>
+        <v>-0.1318</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4718</v>
+        <v>0.4956</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6379</v>
+        <v>-0.0194</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1661</v>
+        <v>0.515</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6343</v>
+        <v>0.2873</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5545</v>
+        <v>1.0003</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0797</v>
+        <v>-0.713</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.1061</v>
+        <v>0.2083</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.1925</v>
+        <v>-1.0197</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9136</v>
+        <v>1.228</v>
       </c>
       <c r="P16" t="n">
+        <v>0.1958</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.1751</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.9585</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.1336</v>
-      </c>
       <c r="S16" t="n">
-        <v>-1.4237</v>
+        <v>-0.045</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5445</v>
+        <v>-0.0218</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1208</v>
+        <v>-0.0232</v>
       </c>
       <c r="V16" t="n">
-        <v>1.159</v>
+        <v>-2.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7673</v>
+        <v>-0.6659</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9339</v>
+        <v>-1.9284</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6556</v>
+        <v>-3.0508</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5895</v>
+        <v>1.1224</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7996</v>
+        <v>-2.4252</v>
       </c>
       <c r="H17" t="n">
-        <v>0.13</v>
+        <v>-0.0452</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9295</v>
+        <v>-2.38</v>
       </c>
       <c r="J17" t="n">
-        <v>1.093</v>
+        <v>-1.217</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0122</v>
+        <v>1.9921</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0808</v>
+        <v>-3.2091</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8926</v>
+        <v>-1.2083</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8822</v>
+        <v>-2.0373</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0104</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4097</v>
+        <v>-0.4824</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2664</v>
+        <v>-0.8546</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6761</v>
+        <v>0.3721</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3599</v>
+        <v>-2.0271</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5625</v>
+        <v>0.3486</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2025</v>
+        <v>-2.3756</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4252</v>
+        <v>-1.7996</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0452</v>
+        <v>0.13</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.38</v>
+        <v>-1.9295</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.217</v>
+        <v>1.093</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9921</v>
+        <v>1.0122</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2091</v>
+        <v>0.0808</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2083</v>
+        <v>-2.8926</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0373</v>
+        <v>-0.8822</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8290999999999999</v>
+        <v>-2.0104</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9139</v>
+        <v>-0.5029</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3662</v>
+        <v>-0.0406</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4523</v>
+        <v>-0.4623</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5707</v>
+        <v>-2.237</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2116</v>
+        <v>-0.9046</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3591</v>
+        <v>-1.3324</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6062</v>
@@ -1936,13 +1936,13 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3562</v>
+        <v>-0.0225</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>0.0694</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1902</v>
+        <v>-3.7809</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7546</v>
+        <v>-0.3453</v>
       </c>
       <c r="F20" t="n">
         <v>-3.4356</v>
@@ -2014,10 +2014,10 @@
         <v>2.1543</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9969</v>
+        <v>-0.5875</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0692</v>
+        <v>-0.6599</v>
       </c>
       <c r="U20" t="n">
         <v>0.0723</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3696</v>
+        <v>-3.8579</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3087</v>
+        <v>-2.797</v>
       </c>
       <c r="F21" t="n">
         <v>-1.061</v>
@@ -2092,10 +2092,10 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6052</v>
+        <v>-0.0935</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6534</v>
+        <v>-0.1417</v>
       </c>
       <c r="U21" t="n">
         <v>0.0482</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4637</v>
+        <v>-6.508</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6773</v>
+        <v>-2.882</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7863</v>
+        <v>-3.626</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1382</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2495</v>
+        <v>-0.2938</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0288</v>
+        <v>-0.1759</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2783</v>
+        <v>-0.1179</v>
       </c>
       <c r="V22" t="n">
         <v>1.2742</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.4216</v>
+        <v>-18.4217</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.135900000000001</v>
+        <v>-4.1359</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.2856</v>
+        <v>-14.2857</v>
       </c>
       <c r="G23" t="n">
         <v>-15.275</v>
@@ -2248,13 +2248,13 @@
         <v>16.647</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.1465</v>
+        <v>-3.1466</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.7702</v>
+        <v>-2.7703</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3764000000000001</v>
+        <v>-0.3765</v>
       </c>
       <c r="V23" t="n">
         <v>9.999999999976694e-05</v>
